--- a/AAII_Financials/Quarterly/SLMT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SLMT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>SLMT</t>
   </si>
@@ -734,10 +734,10 @@
         <v>100</v>
       </c>
       <c r="H8" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="I8" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="J8" s="3">
         <v>300</v>
@@ -769,10 +769,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -804,10 +804,10 @@
         <v>100</v>
       </c>
       <c r="H10" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="I10" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="J10" s="3">
         <v>200</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1006,10 +1006,10 @@
         <v>2400</v>
       </c>
       <c r="H17" s="3">
-        <v>1900</v>
+        <v>1100</v>
       </c>
       <c r="I17" s="3">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="J17" s="3">
         <v>1800</v>
@@ -1041,10 +1041,10 @@
         <v>-2200</v>
       </c>
       <c r="H18" s="3">
-        <v>-1200</v>
+        <v>-800</v>
       </c>
       <c r="I18" s="3">
-        <v>-1300</v>
+        <v>-800</v>
       </c>
       <c r="J18" s="3">
         <v>-1500</v>
@@ -1091,10 +1091,10 @@
         <v>-1200</v>
       </c>
       <c r="H20" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
         <v>-100</v>
@@ -1126,10 +1126,10 @@
         <v>-1000</v>
       </c>
       <c r="H21" s="3">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
       <c r="I21" s="3">
-        <v>-1000</v>
+        <v>-700</v>
       </c>
       <c r="J21" s="3">
         <v>-1400</v>
@@ -1196,10 +1196,10 @@
         <v>-1000</v>
       </c>
       <c r="H23" s="3">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
       <c r="I23" s="3">
-        <v>-1100</v>
+        <v>-700</v>
       </c>
       <c r="J23" s="3">
         <v>-1400</v>
@@ -1230,11 +1230,11 @@
       <c r="G24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>8</v>
@@ -1301,10 +1301,10 @@
         <v>-1000</v>
       </c>
       <c r="H26" s="3">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
       <c r="I26" s="3">
-        <v>-1000</v>
+        <v>-700</v>
       </c>
       <c r="J26" s="3">
         <v>-1400</v>
@@ -1406,10 +1406,10 @@
         <v>-400</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="I29" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="J29" s="3">
         <v>-300</v>
@@ -1511,10 +1511,10 @@
         <v>1200</v>
       </c>
       <c r="H32" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
         <v>100</v>
@@ -1779,10 +1779,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>13800</v>
+        <v>13900</v>
       </c>
       <c r="E43" s="3">
-        <v>13800</v>
+        <v>13900</v>
       </c>
       <c r="F43" s="3">
         <v>2400</v>
@@ -1791,10 +1791,10 @@
         <v>2200</v>
       </c>
       <c r="H43" s="3">
-        <v>1400</v>
+        <v>400</v>
       </c>
       <c r="I43" s="3">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="J43" s="3">
         <v>800</v>
@@ -1825,11 +1825,11 @@
       <c r="G44" s="3">
         <v>0</v>
       </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J44" s="3">
         <v>0</v>
@@ -1860,11 +1860,11 @@
       <c r="G45" s="3">
         <v>0</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
+      <c r="H45" s="3">
+        <v>800</v>
+      </c>
+      <c r="I45" s="3">
+        <v>800</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
@@ -1896,7 +1896,7 @@
         <v>3000</v>
       </c>
       <c r="H46" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="I46" s="3">
         <v>3300</v>
@@ -1930,11 +1930,11 @@
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
-        <v>2600</v>
-      </c>
-      <c r="I47" s="3">
-        <v>2800</v>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J47" s="3">
         <v>100</v>
@@ -1965,11 +1965,11 @@
       <c r="G48" s="3">
         <v>100</v>
       </c>
-      <c r="H48" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I48" s="3">
-        <v>2100</v>
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J48" s="3">
         <v>1200</v>
@@ -2001,10 +2001,10 @@
         <v>27400</v>
       </c>
       <c r="H49" s="3">
-        <v>2900</v>
+        <v>900</v>
       </c>
       <c r="I49" s="3">
-        <v>3100</v>
+        <v>1000</v>
       </c>
       <c r="J49" s="3">
         <v>4100</v>
@@ -2105,11 +2105,11 @@
       <c r="G52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
+      <c r="H52" s="3">
+        <v>6500</v>
+      </c>
+      <c r="I52" s="3">
+        <v>7000</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>8</v>
@@ -2241,10 +2241,10 @@
         <v>7100</v>
       </c>
       <c r="H57" s="3">
-        <v>3300</v>
+        <v>1500</v>
       </c>
       <c r="I57" s="3">
-        <v>3600</v>
+        <v>1600</v>
       </c>
       <c r="J57" s="3">
         <v>3000</v>
@@ -2276,10 +2276,10 @@
         <v>2800</v>
       </c>
       <c r="H58" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>300</v>
@@ -2311,10 +2311,10 @@
         <v>300</v>
       </c>
       <c r="H59" s="3">
-        <v>300</v>
+        <v>2800</v>
       </c>
       <c r="I59" s="3">
-        <v>300</v>
+        <v>3100</v>
       </c>
       <c r="J59" s="3">
         <v>300</v>
@@ -2381,10 +2381,10 @@
         <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
         <v>800</v>
@@ -2416,10 +2416,10 @@
         <v>5300</v>
       </c>
       <c r="H62" s="3">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="I62" s="3">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="J62" s="3">
         <v>1400</v>
@@ -3034,10 +3034,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -3045,8 +3045,8 @@
       <c r="G83" s="3">
         <v>0</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
@@ -3635,8 +3635,8 @@
       <c r="G101" s="3">
         <v>0</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I101" s="3">
         <v>0</v>
